--- a/data/trans_camb/IP17-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 9,03</t>
+          <t>-11,24; 8,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 23,01</t>
+          <t>-2,04; 21,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,63; 1,68</t>
+          <t>-19,7; 0,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 7,23</t>
+          <t>-14,6; 5,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 3,73</t>
+          <t>-17,12; 4,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 3,37</t>
+          <t>-17,83; 2,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 4,91</t>
+          <t>-9,18; 4,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 9,24</t>
+          <t>-6,71; 8,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,63; -1,78</t>
+          <t>-16,26; -1,14</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,79; 56,14</t>
+          <t>-41,65; 52,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 134,0</t>
+          <t>-9,41; 123,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-74,97; 12,53</t>
+          <t>-73,73; 3,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 40,59</t>
+          <t>-48,73; 31,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,27; 23,04</t>
+          <t>-58,56; 25,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,81; 18,94</t>
+          <t>-64,46; 19,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,35; 25,95</t>
+          <t>-36,48; 26,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 48,27</t>
+          <t>-24,75; 45,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,34; -6,42</t>
+          <t>-62,62; -5,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,48</t>
+          <t>-1,36; 7,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 4,65</t>
+          <t>-3,64; 4,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,78; -0,57</t>
+          <t>-9,36; -0,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 7,02</t>
+          <t>-1,84; 7,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 1,54</t>
+          <t>-6,62; 1,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -0,46</t>
+          <t>-9,08; -0,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,96</t>
+          <t>-0,73; 5,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,84</t>
+          <t>-4,23; 2,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -1,8</t>
+          <t>-7,9; -1,6</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 44,87</t>
+          <t>-6,04; 43,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 27,71</t>
+          <t>-17,16; 28,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,01; -2,72</t>
+          <t>-44,81; -3,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 34,55</t>
+          <t>-7,52; 35,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 7,39</t>
+          <t>-27,28; 8,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,8; -2,07</t>
+          <t>-37,72; -2,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 30,53</t>
+          <t>-3,36; 29,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 9,57</t>
+          <t>-18,45; 10,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,91; -8,94</t>
+          <t>-35,54; -7,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 15,19</t>
+          <t>-0,58; 15,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 5,62</t>
+          <t>-8,47; 5,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 5,52</t>
+          <t>-8,75; 5,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 2,65</t>
+          <t>-11,44; 2,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 5,09</t>
+          <t>-10,03; 4,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 1,99</t>
+          <t>-12,66; 2,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 6,24</t>
+          <t>-3,41; 6,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,81</t>
+          <t>-6,97; 2,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 1,62</t>
+          <t>-8,29; 1,87</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 94,05</t>
+          <t>-3,69; 90,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 34,47</t>
+          <t>-35,59; 31,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 34,58</t>
+          <t>-40,35; 36,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 13,6</t>
+          <t>-44,03; 13,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 26,72</t>
+          <t>-36,83; 22,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 13,44</t>
+          <t>-48,87; 11,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 33,97</t>
+          <t>-15,27; 34,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 22,09</t>
+          <t>-28,43; 15,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,03; 9,22</t>
+          <t>-36,62; 10,01</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 7,06</t>
+          <t>-0,03; 6,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,06</t>
+          <t>-2,53; 4,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,98; -0,82</t>
+          <t>-8,25; -0,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,01</t>
+          <t>-3,58; 3,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 0,66</t>
+          <t>-5,93; 0,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -2,07</t>
+          <t>-9,24; -2,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,4</t>
+          <t>-1,0; 4,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,6</t>
+          <t>-3,51; 1,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -2,11</t>
+          <t>-7,41; -2,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 39,19</t>
+          <t>-0,15; 38,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 22,67</t>
+          <t>-12,08; 22,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,64; -4,66</t>
+          <t>-38,31; -2,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 18,92</t>
+          <t>-14,71; 17,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 3,19</t>
+          <t>-24,43; 4,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,87; -9,97</t>
+          <t>-36,88; -9,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 22,32</t>
+          <t>-4,39; 20,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 8,01</t>
+          <t>-15,68; 7,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,63; -11,08</t>
+          <t>-32,94; -12,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 8,97</t>
+          <t>-10,32; 9,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 21,73</t>
+          <t>-1,0; 24,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 0,42</t>
+          <t>-19,38; 0,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 5,91</t>
+          <t>-13,31; 6,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 4,14</t>
+          <t>-17,7; 5,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 2,92</t>
+          <t>-18,77; 3,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 4,91</t>
+          <t>-9,47; 4,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 8,95</t>
+          <t>-5,82; 9,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -1,14</t>
+          <t>-16,67; -1,15</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 52,0</t>
+          <t>-38,4; 57,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 123,61</t>
+          <t>-6,17; 136,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,73; 3,16</t>
+          <t>-73,65; 4,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 31,45</t>
+          <t>-46,25; 37,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 25,47</t>
+          <t>-58,97; 32,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,46; 19,02</t>
+          <t>-67,97; 18,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 26,58</t>
+          <t>-35,13; 22,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 45,79</t>
+          <t>-22,23; 48,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-62,62; -5,65</t>
+          <t>-63,06; -5,93</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 7,47</t>
+          <t>-1,49; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 4,9</t>
+          <t>-3,28; 5,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,36; -0,53</t>
+          <t>-9,89; -0,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 7,23</t>
+          <t>-1,9; 7,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 1,82</t>
+          <t>-6,86; 2,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; -0,55</t>
+          <t>-8,82; 0,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,73</t>
+          <t>-0,4; 5,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 2,02</t>
+          <t>-4,3; 1,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -1,6</t>
+          <t>-7,54; -1,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 43,29</t>
+          <t>-7,64; 41,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 28,61</t>
+          <t>-15,27; 30,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,81; -3,28</t>
+          <t>-45,81; -2,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 35,61</t>
+          <t>-8,14; 34,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 8,72</t>
+          <t>-28,55; 9,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,72; -2,74</t>
+          <t>-35,55; 0,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 29,88</t>
+          <t>-1,84; 28,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 10,29</t>
+          <t>-19,61; 10,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,54; -7,61</t>
+          <t>-33,67; -6,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 15,04</t>
+          <t>-0,33; 13,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 5,46</t>
+          <t>-7,68; 5,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 5,82</t>
+          <t>-8,43; 5,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 2,46</t>
+          <t>-10,84; 3,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 4,3</t>
+          <t>-9,97; 4,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 2,0</t>
+          <t>-13,1; 1,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,41</t>
+          <t>-3,79; 6,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 2,83</t>
+          <t>-6,68; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 1,87</t>
+          <t>-8,71; 1,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 90,36</t>
+          <t>-2,18; 80,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 31,9</t>
+          <t>-35,09; 34,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 36,36</t>
+          <t>-35,93; 32,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,03; 13,96</t>
+          <t>-42,41; 20,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,83; 22,47</t>
+          <t>-38,22; 26,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 11,62</t>
+          <t>-51,06; 9,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 34,36</t>
+          <t>-16,04; 37,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 15,65</t>
+          <t>-27,93; 17,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 10,01</t>
+          <t>-37,01; 6,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 6,95</t>
+          <t>-0,0; 7,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,08</t>
+          <t>-2,5; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; -0,59</t>
+          <t>-8,16; -0,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,78</t>
+          <t>-3,6; 3,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,79</t>
+          <t>-6,14; 0,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -2,03</t>
+          <t>-8,58; -1,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,16</t>
+          <t>-0,69; 4,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,51</t>
+          <t>-3,37; 1,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -2,38</t>
+          <t>-7,24; -2,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 38,51</t>
+          <t>0,04; 39,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 22,6</t>
+          <t>-11,5; 24,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-38,31; -2,92</t>
+          <t>-39,31; -5,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 17,97</t>
+          <t>-14,82; 18,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 4,0</t>
+          <t>-24,94; 4,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,88; -9,49</t>
+          <t>-35,69; -7,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 20,79</t>
+          <t>-3,0; 21,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 7,63</t>
+          <t>-15,18; 6,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,94; -12,3</t>
+          <t>-32,32; -12,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP17-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP17-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-7,72</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,01</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10,4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-10,02</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,09</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,53</t>
+          <t>-9,25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-9,15</t>
+          <t>-8,31</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 9,87</t>
+          <t>-14,33; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 24,02</t>
+          <t>-17,65; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 0,69</t>
+          <t>-18,32; 4,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 6,55</t>
+          <t>-10,93; 9,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 5,39</t>
+          <t>-1,04; 23,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 3,22</t>
+          <t>-18,67; 2,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 4,41</t>
+          <t>-9,57; 4,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 9,69</t>
+          <t>-6,11; 9,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -1,15</t>
+          <t>-15,53; -0,7</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-15,22%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-25,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-32,51%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-4,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>47,29%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-45,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-15,22%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-25,65%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,93%</t>
+          <t>-42,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-40,06%</t>
+          <t>-36,36%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 57,22</t>
+          <t>-47,18; 40,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 136,59</t>
+          <t>-58,27; 23,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 4,17</t>
+          <t>-65,22; 24,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 37,34</t>
+          <t>-41,79; 56,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,97; 32,35</t>
+          <t>-4,85; 134,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 18,73</t>
+          <t>-71,87; 15,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 22,78</t>
+          <t>-36,35; 25,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 48,97</t>
+          <t>-23,69; 48,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,06; -5,93</t>
+          <t>-58,42; -1,97</t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,33</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,6</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,07</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,61</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,67</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,33</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>-4,43</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,78</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>-4,55</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 7,06</t>
+          <t>-1,72; 7,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 5,23</t>
+          <t>-6,7; 1,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; -0,45</t>
+          <t>-9,07; -0,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,0</t>
+          <t>-1,61; 7,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 2,08</t>
+          <t>-3,75; 4,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 0,04</t>
+          <t>-8,83; -0,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,59</t>
+          <t>-0,25; 5,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,96</t>
+          <t>-4,34; 1,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; -1,24</t>
+          <t>-7,63; -1,63</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,49%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-20,7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-24,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,49%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,5%</t>
+          <t>-23,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-22,27%</t>
+          <t>-21,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 41,17</t>
+          <t>-7,2; 34,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 30,71</t>
+          <t>-27,68; 7,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -2,31</t>
+          <t>-37,68; -2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 34,97</t>
+          <t>-7,54; 44,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,55; 9,79</t>
+          <t>-17,11; 27,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 0,56</t>
+          <t>-41,63; -1,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 28,86</t>
+          <t>-1,25; 30,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 10,05</t>
+          <t>-19,28; 9,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,67; -6,06</t>
+          <t>-34,05; -8,47</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,21</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-5,17</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>6,68</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,17</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,21</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,43</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-3,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 13,73</t>
+          <t>-11,82; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 5,71</t>
+          <t>-9,26; 5,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 5,69</t>
+          <t>-12,71; 2,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 3,42</t>
+          <t>-0,42; 15,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 4,82</t>
+          <t>-8,12; 5,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 1,7</t>
+          <t>-9,08; 4,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,95</t>
+          <t>-4,16; 6,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 3,44</t>
+          <t>-6,63; 3,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 1,26</t>
+          <t>-8,71; 1,35</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-18,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-10,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-23,21%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>33,98%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-5,97%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,4%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-18,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-10,0%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,36%</t>
+          <t>-10,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,07%</t>
+          <t>-17,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 80,89</t>
+          <t>-44,77; 13,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,09; 34,44</t>
+          <t>-36,65; 26,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 32,93</t>
+          <t>-47,96; 14,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 20,05</t>
+          <t>-2,16; 94,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 26,67</t>
+          <t>-36,19; 34,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 9,6</t>
+          <t>-38,97; 27,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 37,7</t>
+          <t>-18,02; 33,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,93; 17,27</t>
+          <t>-27,69; 22,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 6,94</t>
+          <t>-37,83; 6,95</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,69</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,05</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,85</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,51</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,69</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>-4,41</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,79</t>
+          <t>-4,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 7,06</t>
+          <t>-3,17; 4,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,47</t>
+          <t>-6,26; 0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -0,94</t>
+          <t>-9,0; -1,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,84</t>
+          <t>-0,3; 7,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 0,91</t>
+          <t>-2,89; 4,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -1,52</t>
+          <t>-7,87; -0,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,27</t>
+          <t>-0,71; 4,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,39</t>
+          <t>-3,45; 1,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; -2,45</t>
+          <t>-7,28; -2,2</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-12,01%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-22,52%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>17,15%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-22,97%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-12,01%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-22,96%</t>
+          <t>-22,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-22,76%</t>
+          <t>-22,38%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 39,78</t>
+          <t>-13,28; 18,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 24,5</t>
+          <t>-25,66; 3,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,31; -5,96</t>
+          <t>-37,11; -9,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 18,58</t>
+          <t>-1,36; 39,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 4,47</t>
+          <t>-13,2; 22,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,69; -7,52</t>
+          <t>-36,43; -4,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 21,53</t>
+          <t>-3,18; 22,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 6,85</t>
+          <t>-15,36; 8,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -12,13</t>
+          <t>-31,98; -10,78</t>
         </is>
       </c>
     </row>
